--- a/docs/assets/cases/rules-independent.xlsx
+++ b/docs/assets/cases/rules-independent.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="154">
   <si>
     <t>selected_count</t>
   </si>
@@ -117,7 +117,7 @@
     <t>["EXT_SOURCE_2", "EXT_SOURCE_3"]</t>
   </si>
   <si>
-    <t>"cccd15c5-8fbd-41aa-a82b-f9656e078448"</t>
+    <t>"408b6056-e5a0-4558-88d4-98cbbc56b0ea"</t>
   </si>
   <si>
     <t>rule_id</t>
@@ -291,12 +291,15 @@
     <t>display_name</t>
   </si>
   <si>
+    <t>dtype</t>
+  </si>
+  <si>
+    <t>data_source</t>
+  </si>
+  <si>
     <t>description</t>
   </si>
   <si>
-    <t>data_source</t>
-  </si>
-  <si>
     <t>unit</t>
   </si>
   <si>
@@ -306,12 +309,12 @@
     <t>外部来源分 3</t>
   </si>
   <si>
+    <t>Home Credit 2018 application_{train|test}.csv</t>
+  </si>
+  <si>
     <t>Normalized score from external data source</t>
   </si>
   <si>
-    <t>Home Credit 2018 application_{train|test}.csv</t>
-  </si>
-  <si>
     <t>归一化值（无量纲）</t>
   </si>
   <si>
@@ -453,7 +456,7 @@
     <t>maturity</t>
   </si>
   <si>
-    <t>"e22c5e61-6570-45f5-9b50-d188fbc5c81c"</t>
+    <t>"050120ae-8498-4d2f-b5b8-c32c27da38c7"</t>
   </si>
   <si>
     <t>"rule"</t>
@@ -465,7 +468,7 @@
     <t>{"summary":{"rows":1,"grain":"one mining run (or benchmark summary); no feature-level metrics","schema_version":1,"fields":{"selected_count":{"dtype":"Int64","unit":"count","meaning":"最终 RuleSet 中入选规则数；no_rules 为 0","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_query":"unsupported"},"rules":{"rows":1,"grain":"final rule_id / selection rank; grades are rule membership, not metrics","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"expression":{"dtype":"String","unit":"definition","meaning":"既有 DSL 规范表达式；不执行报告文本","null":"unavailable; inspect status and report parameters"},"rank":{"dtype":"Int64","unit":"ordinal","meaning":"最终规则集的 1 起始顺序；cumulative 使用此前全部规则的并集","null":"unavailable; inspect status and report parameters"},"source":{"dtype":"String","unit":"category","meaning":"规则生成来源；不是业务特征来源","null":"unavailable; inspect status and report parameters"},"labels":{"dtype":"List(String)","unit":"unknown","meaning":"已保存的 labels；未登记业务含义保持 unknown","null":"unavailable; inspect status and report parameters"},"grades":{"dtype":"List(String)","unit":"category","meaning":"既有 RuleSet 等级成员列表","null":"unavailable; inspect status and report parameters"},"generation_round":{"dtype":"Int64","unit":"ordinal","meaning":"候选生成轮次；相同规则在不同轮次的审计不可合并","null":"unavailable; inspect status and report parameters"},"selection_round":{"dtype":"Int64","unit":"ordinal","meaning":"实际 cascade 入选轮次；未入选为 null","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"evaluation":{"rows":3,"grain":"dataset / rule_id / target / slice / group (hit, miss, total)","schema_version":1,"fields":{"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"total_count":{"dtype":"Int64","unit":"count","meaning":"当前范围全部样本人数，包括当前 target 未观测的样本","null":"unavailable; inspect status and report parameters"},"observed_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已观测人数，与 sample_count 相同","null":"unavailable; inspect status and report parameters"},"unobserved_count":{"dtype":"Int64","unit":"count","meaning":"total_count 减 observed_count；不把未观测当好样本","null":"unavailable; inspect status and report parameters"},"distribution_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 total_count / 同 dataset、target、slice 的总体人数","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"event_amount":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现 label=1 金额和；amount_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"amount_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前 amount_total / 同范围 base amount_total","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"amount_event_rate / 同范围 base amount_event_rate","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"event_customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现 label=1 范围去重客户数","null":"unavailable; inspect status and report parameters"},"customer_coverage":{"dtype":"Null","unit":"ratio","meaning":"customer_count / 同范围 base customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_lift":{"dtype":"Null","unit":"dimensionless","meaning":"customer_event_rate / 同范围 base customer_event_rate","null":"unavailable; inspect status and report parameters"},"event_rate_ci_lower":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间下界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"event_rate_ci_upper":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间上界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"slices":{"rows":15,"grain":"dataset / rule_id / target / slice / group; slice encodes supplied time or segment","schema_version":1,"fields":{"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"total_count":{"dtype":"Int64","unit":"count","meaning":"当前范围全部样本人数，包括当前 target 未观测的样本","null":"unavailable; inspect status and report parameters"},"observed_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已观测人数，与 sample_count 相同","null":"unavailable; inspect status and report parameters"},"unobserved_count":{"dtype":"Int64","unit":"count","meaning":"total_count 减 observed_count；不把未观测当好样本","null":"unavailable; inspect status and report parameters"},"distribution_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 total_count / 同 dataset、target、slice 的总体人数","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"event_amount":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现 label=1 金额和；amount_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"amount_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前 amount_total / 同范围 base amount_total","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"amount_event_rate / 同范围 base amount_event_rate","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"event_customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现 label=1 范围去重客户数","null":"unavailable; inspect status and report parameters"},"customer_coverage":{"dtype":"Null","unit":"ratio","meaning":"customer_count / 同范围 base customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_lift":{"dtype":"Null","unit":"dimensionless","meaning":"customer_event_rate / 同范围 base customer_event_rate","null":"unavailable; inspect status and report parameters"},"event_rate_ci_lower":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间下界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"event_rate_ci_upper":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间上界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"rule_features":{"rows":2,"grain":"distinct rule_id / English feature; includes rejected candidates","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"feature":{"dtype":"String","unit":"identifier","meaning":"AST 提取的英文输入特征 ID；中文名不替代此身份","null":"unavailable; inspect status and report parameters"}},"feature_roles":{"feature":"feature"},"state":"computed","feature_query":"direct"}}</t>
   </si>
   <si>
-    <t>{"dataset":"fixed_all_partitions","primary_target":"TARGET","targets":["TARGET"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"batch_size":100,"direction":"high_risk","confidence_level":0.95,"compute_statistics":true,"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"selection_report_id":"cccd15c5-8fbd-41aa-a82b-f9656e078448","fixed_rule_set":true}</t>
+    <t>{"dataset":"fixed_all_partitions","primary_target":"TARGET","targets":["TARGET"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"batch_size":100,"direction":"high_risk","confidence_level":0.95,"compute_statistics":true,"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"selection_report_id":"408b6056-e5a0-4558-88d4-98cbbc56b0ea","fixed_rule_set":true}</t>
   </si>
   <si>
     <t>{"dataset_id":"home-credit-default-risk-2018","computation":"rule","producer":"mars.rule.MarsRuleReport","mars_version":"unknown","origin_project":"unknown"}</t>
@@ -2401,10 +2404,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -2420,16 +2423,16 @@
       <c r="E1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
         <v>95</v>
@@ -2437,15 +2440,15 @@
       <c r="E2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" t="s">
         <v>94</v>
       </c>
       <c r="D3" t="s">
@@ -2453,6 +2456,9 @@
       </c>
       <c r="E3" t="s">
         <v>96</v>
+      </c>
+      <c r="F3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2473,18 +2479,18 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2495,10 +2501,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2509,10 +2515,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2523,10 +2529,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2540,7 +2546,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2551,10 +2557,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2568,7 +2574,7 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2579,10 +2585,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2593,10 +2599,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2607,10 +2613,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2621,7 +2627,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -2635,10 +2641,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2649,10 +2655,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2663,10 +2669,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2680,7 +2686,7 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2691,10 +2697,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2705,10 +2711,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2719,10 +2725,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2733,10 +2739,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2747,10 +2753,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2777,18 +2783,18 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2799,10 +2805,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2813,10 +2819,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2827,10 +2833,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2841,10 +2847,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2858,7 +2864,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2869,7 +2875,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" t="s">
         <v>43</v>
@@ -2883,10 +2889,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2897,10 +2903,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2911,10 +2917,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2925,10 +2931,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12">
         <v>1</v>

--- a/docs/assets/cases/rules-independent.xlsx
+++ b/docs/assets/cases/rules-independent.xlsx
@@ -117,7 +117,7 @@
     <t>["EXT_SOURCE_2", "EXT_SOURCE_3"]</t>
   </si>
   <si>
-    <t>"408b6056-e5a0-4558-88d4-98cbbc56b0ea"</t>
+    <t>"57f3678d-f9b3-4d5c-86f8-9c36843f32d3"</t>
   </si>
   <si>
     <t>rule_id</t>
@@ -456,7 +456,7 @@
     <t>maturity</t>
   </si>
   <si>
-    <t>"050120ae-8498-4d2f-b5b8-c32c27da38c7"</t>
+    <t>"3a407860-8766-4e2b-a51d-09856f2483a9"</t>
   </si>
   <si>
     <t>"rule"</t>
@@ -468,7 +468,7 @@
     <t>{"summary":{"rows":1,"grain":"one mining run (or benchmark summary); no feature-level metrics","schema_version":1,"fields":{"selected_count":{"dtype":"Int64","unit":"count","meaning":"最终 RuleSet 中入选规则数；no_rules 为 0","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_query":"unsupported"},"rules":{"rows":1,"grain":"final rule_id / selection rank; grades are rule membership, not metrics","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"expression":{"dtype":"String","unit":"definition","meaning":"既有 DSL 规范表达式；不执行报告文本","null":"unavailable; inspect status and report parameters"},"rank":{"dtype":"Int64","unit":"ordinal","meaning":"最终规则集的 1 起始顺序；cumulative 使用此前全部规则的并集","null":"unavailable; inspect status and report parameters"},"source":{"dtype":"String","unit":"category","meaning":"规则生成来源；不是业务特征来源","null":"unavailable; inspect status and report parameters"},"labels":{"dtype":"List(String)","unit":"unknown","meaning":"已保存的 labels；未登记业务含义保持 unknown","null":"unavailable; inspect status and report parameters"},"grades":{"dtype":"List(String)","unit":"category","meaning":"既有 RuleSet 等级成员列表","null":"unavailable; inspect status and report parameters"},"generation_round":{"dtype":"Int64","unit":"ordinal","meaning":"候选生成轮次；相同规则在不同轮次的审计不可合并","null":"unavailable; inspect status and report parameters"},"selection_round":{"dtype":"Int64","unit":"ordinal","meaning":"实际 cascade 入选轮次；未入选为 null","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"evaluation":{"rows":3,"grain":"dataset / rule_id / target / slice / group (hit, miss, total)","schema_version":1,"fields":{"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"total_count":{"dtype":"Int64","unit":"count","meaning":"当前范围全部样本人数，包括当前 target 未观测的样本","null":"unavailable; inspect status and report parameters"},"observed_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已观测人数，与 sample_count 相同","null":"unavailable; inspect status and report parameters"},"unobserved_count":{"dtype":"Int64","unit":"count","meaning":"total_count 减 observed_count；不把未观测当好样本","null":"unavailable; inspect status and report parameters"},"distribution_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 total_count / 同 dataset、target、slice 的总体人数","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"event_amount":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现 label=1 金额和；amount_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"amount_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前 amount_total / 同范围 base amount_total","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"amount_event_rate / 同范围 base amount_event_rate","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"event_customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现 label=1 范围去重客户数","null":"unavailable; inspect status and report parameters"},"customer_coverage":{"dtype":"Null","unit":"ratio","meaning":"customer_count / 同范围 base customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_lift":{"dtype":"Null","unit":"dimensionless","meaning":"customer_event_rate / 同范围 base customer_event_rate","null":"unavailable; inspect status and report parameters"},"event_rate_ci_lower":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间下界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"event_rate_ci_upper":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间上界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"slices":{"rows":15,"grain":"dataset / rule_id / target / slice / group; slice encodes supplied time or segment","schema_version":1,"fields":{"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"total_count":{"dtype":"Int64","unit":"count","meaning":"当前范围全部样本人数，包括当前 target 未观测的样本","null":"unavailable; inspect status and report parameters"},"observed_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已观测人数，与 sample_count 相同","null":"unavailable; inspect status and report parameters"},"unobserved_count":{"dtype":"Int64","unit":"count","meaning":"total_count 减 observed_count；不把未观测当好样本","null":"unavailable; inspect status and report parameters"},"distribution_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 total_count / 同 dataset、target、slice 的总体人数","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"event_amount":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现 label=1 金额和；amount_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"amount_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前 amount_total / 同范围 base amount_total","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"amount_event_rate / 同范围 base amount_event_rate","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"event_customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现 label=1 范围去重客户数","null":"unavailable; inspect status and report parameters"},"customer_coverage":{"dtype":"Null","unit":"ratio","meaning":"customer_count / 同范围 base customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_lift":{"dtype":"Null","unit":"dimensionless","meaning":"customer_event_rate / 同范围 base customer_event_rate","null":"unavailable; inspect status and report parameters"},"event_rate_ci_lower":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间下界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"event_rate_ci_upper":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间上界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"rule_features":{"rows":2,"grain":"distinct rule_id / English feature; includes rejected candidates","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"feature":{"dtype":"String","unit":"identifier","meaning":"AST 提取的英文输入特征 ID；中文名不替代此身份","null":"unavailable; inspect status and report parameters"}},"feature_roles":{"feature":"feature"},"state":"computed","feature_query":"direct"}}</t>
   </si>
   <si>
-    <t>{"dataset":"fixed_all_partitions","primary_target":"TARGET","targets":["TARGET"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"batch_size":100,"direction":"high_risk","confidence_level":0.95,"compute_statistics":true,"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"selection_report_id":"408b6056-e5a0-4558-88d4-98cbbc56b0ea","fixed_rule_set":true}</t>
+    <t>{"dataset":"fixed_all_partitions","primary_target":"TARGET","targets":["TARGET"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"batch_size":100,"direction":"high_risk","confidence_level":0.95,"compute_statistics":true,"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"selection_report_id":"57f3678d-f9b3-4d5c-86f8-9c36843f32d3","fixed_rule_set":true}</t>
   </si>
   <si>
     <t>{"dataset_id":"home-credit-default-risk-2018","computation":"rule","producer":"mars.rule.MarsRuleReport","mars_version":"unknown","origin_project":"unknown"}</t>

--- a/docs/assets/cases/rules-independent.xlsx
+++ b/docs/assets/cases/rules-independent.xlsx
@@ -117,7 +117,7 @@
     <t>["EXT_SOURCE_2", "EXT_SOURCE_3"]</t>
   </si>
   <si>
-    <t>"57f3678d-f9b3-4d5c-86f8-9c36843f32d3"</t>
+    <t>"dc3aa22f-37ad-4b2e-8872-9fbda42bcb4b"</t>
   </si>
   <si>
     <t>rule_id</t>
@@ -456,7 +456,7 @@
     <t>maturity</t>
   </si>
   <si>
-    <t>"3a407860-8766-4e2b-a51d-09856f2483a9"</t>
+    <t>"9abc0b71-fd5c-4528-b643-1aa44655b9ee"</t>
   </si>
   <si>
     <t>"rule"</t>
@@ -468,7 +468,7 @@
     <t>{"summary":{"rows":1,"grain":"one mining run (or benchmark summary); no feature-level metrics","schema_version":1,"fields":{"selected_count":{"dtype":"Int64","unit":"count","meaning":"最终 RuleSet 中入选规则数；no_rules 为 0","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_query":"unsupported"},"rules":{"rows":1,"grain":"final rule_id / selection rank; grades are rule membership, not metrics","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"expression":{"dtype":"String","unit":"definition","meaning":"既有 DSL 规范表达式；不执行报告文本","null":"unavailable; inspect status and report parameters"},"rank":{"dtype":"Int64","unit":"ordinal","meaning":"最终规则集的 1 起始顺序；cumulative 使用此前全部规则的并集","null":"unavailable; inspect status and report parameters"},"source":{"dtype":"String","unit":"category","meaning":"规则生成来源；不是业务特征来源","null":"unavailable; inspect status and report parameters"},"labels":{"dtype":"List(String)","unit":"unknown","meaning":"已保存的 labels；未登记业务含义保持 unknown","null":"unavailable; inspect status and report parameters"},"grades":{"dtype":"List(String)","unit":"category","meaning":"既有 RuleSet 等级成员列表","null":"unavailable; inspect status and report parameters"},"generation_round":{"dtype":"Int64","unit":"ordinal","meaning":"候选生成轮次；相同规则在不同轮次的审计不可合并","null":"unavailable; inspect status and report parameters"},"selection_round":{"dtype":"Int64","unit":"ordinal","meaning":"实际 cascade 入选轮次；未入选为 null","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"evaluation":{"rows":3,"grain":"dataset / rule_id / target / slice / group (hit, miss, total)","schema_version":1,"fields":{"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"total_count":{"dtype":"Int64","unit":"count","meaning":"当前范围全部样本人数，包括当前 target 未观测的样本","null":"unavailable; inspect status and report parameters"},"observed_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已观测人数，与 sample_count 相同","null":"unavailable; inspect status and report parameters"},"unobserved_count":{"dtype":"Int64","unit":"count","meaning":"total_count 减 observed_count；不把未观测当好样本","null":"unavailable; inspect status and report parameters"},"distribution_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 total_count / 同 dataset、target、slice 的总体人数","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"event_amount":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现 label=1 金额和；amount_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"amount_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前 amount_total / 同范围 base amount_total","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"amount_event_rate / 同范围 base amount_event_rate","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"event_customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现 label=1 范围去重客户数","null":"unavailable; inspect status and report parameters"},"customer_coverage":{"dtype":"Null","unit":"ratio","meaning":"customer_count / 同范围 base customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_lift":{"dtype":"Null","unit":"dimensionless","meaning":"customer_event_rate / 同范围 base customer_event_rate","null":"unavailable; inspect status and report parameters"},"event_rate_ci_lower":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间下界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"event_rate_ci_upper":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间上界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"slices":{"rows":15,"grain":"dataset / rule_id / target / slice / group; slice encodes supplied time or segment","schema_version":1,"fields":{"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"total_count":{"dtype":"Int64","unit":"count","meaning":"当前范围全部样本人数，包括当前 target 未观测的样本","null":"unavailable; inspect status and report parameters"},"observed_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已观测人数，与 sample_count 相同","null":"unavailable; inspect status and report parameters"},"unobserved_count":{"dtype":"Int64","unit":"count","meaning":"total_count 减 observed_count；不把未观测当好样本","null":"unavailable; inspect status and report parameters"},"distribution_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 total_count / 同 dataset、target、slice 的总体人数","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；评估 ok/unobserved/empty；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"event_amount":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现 label=1 金额和；amount_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"amount_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前 amount_total / 同范围 base amount_total","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"amount_event_rate / 同范围 base amount_event_rate","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"event_customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现 label=1 范围去重客户数","null":"unavailable; inspect status and report parameters"},"customer_coverage":{"dtype":"Null","unit":"ratio","meaning":"customer_count / 同范围 base customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_lift":{"dtype":"Null","unit":"dimensionless","meaning":"customer_event_rate / 同范围 base customer_event_rate","null":"unavailable; inspect status and report parameters"},"event_rate_ci_lower":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间下界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"event_rate_ci_upper":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间上界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"rule_features":{"rows":2,"grain":"distinct rule_id / English feature; includes rejected candidates","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"feature":{"dtype":"String","unit":"identifier","meaning":"AST 提取的英文输入特征 ID；中文名不替代此身份","null":"unavailable; inspect status and report parameters"}},"feature_roles":{"feature":"feature"},"state":"computed","feature_query":"direct"}}</t>
   </si>
   <si>
-    <t>{"dataset":"fixed_all_partitions","primary_target":"TARGET","targets":["TARGET"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"batch_size":100,"direction":"high_risk","confidence_level":0.95,"compute_statistics":true,"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"selection_report_id":"57f3678d-f9b3-4d5c-86f8-9c36843f32d3","fixed_rule_set":true}</t>
+    <t>{"dataset":"fixed_all_partitions","primary_target":"TARGET","targets":["TARGET"],"group_col":"dataset_flag","time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"batch_size":100,"direction":"high_risk","confidence_level":0.95,"compute_statistics":true,"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"selection_report_id":"dc3aa22f-37ad-4b2e-8872-9fbda42bcb4b","fixed_rule_set":true}</t>
   </si>
   <si>
     <t>{"dataset_id":"home-credit-default-risk-2018","computation":"rule","producer":"mars.rule.MarsRuleReport","mars_version":"unknown","origin_project":"unknown"}</t>
